--- a/public/plantillas/Template_Carga_Masiva_PRCP.xlsx
+++ b/public/plantillas/Template_Carga_Masiva_PRCP.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Proyectos\FrontendGoreSM\frontend-dashboardgoresm\public\plantillas\Plantillas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Proyectos\CargaMasiva\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F710E8F2-480D-402C-9562-2A037EE54696}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDD350DD-21D3-45BF-8477-409AE17A2927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_PRCP_INDICADOR_VALOR" sheetId="1" r:id="rId1"/>
@@ -294,9 +294,6 @@
     <t>VALOR</t>
   </si>
   <si>
-    <t>[2023 - 2026]</t>
-  </si>
-  <si>
     <t>U001</t>
   </si>
   <si>
@@ -336,7 +333,10 @@
     <t>META</t>
   </si>
   <si>
-    <t>Meta</t>
+    <t>2023-2026</t>
+  </si>
+  <si>
+    <t>Línea de base</t>
   </si>
 </sst>
 </file>
@@ -673,46 +673,46 @@
         <v>89</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>103</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>104</v>
@@ -735,15 +735,18 @@
       <c r="X2" s="4"/>
     </row>
   </sheetData>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation type="list" sqref="A2:A201" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"VALOR"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="O2:O201" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"META,BASE"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="P2:P201" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" sqref="P3:P201" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"Meta,Linea de base"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="P2" xr:uid="{E5FA6D2E-A7BC-4B33-8508-A34BA5182D47}">
+      <formula1>"Meta,Línea de base"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
